--- a/reports/Product_Analysis_Report.xlsx
+++ b/reports/Product_Analysis_Report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameter Comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameter Comparison'!$A$1:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Parameter Comparison'!$A$1:$W$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C6500"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
@@ -61,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -137,19 +146,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -517,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -733,29 +748,25 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>No business change detected; parameters remain unchanged.</t>
+          <t>Unable to generate summary.</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>No business change detected; parameters remain unchanged.</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>Since there is no change in the parameters, there is no impact on business processes or operations.</t>
-        </is>
-      </c>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="W3" s="5" t="n">
@@ -788,22 +799,524 @@
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>98.81999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>99.41</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>This is a non-linked, life, individual, non-participating, single/regular premium payment, savings plan available on single and joint life basis and prashil wanjari business analyst
+b) The plan provides death benefit during the Policy Term (PT) (under all variants), maturity benefit (under all Variant), Income Benefit after Premium Payment Term (PPT) plus Deferment Period (DP) (under Variants 1, 2, 3 ,4 &amp; 6) and surrender value (under all variants). All these benefits are detailed further in the sections below.
+The product has six (6) variants. i) Variant 1 – Lifelong Income: 1. The variant has a limited/regular premium payment option with Single life. The life cover is available during the policy term. On death of the life assured, the death benefit in instalments (as mentioned in the Benefits section below) will be paid, the policy will be terminated, and no further benefit is payable
+2. At the end of the deferment period, provided the life assured is alive then, the Income Benefit is paid as instalments over the Income Period up to age 120 years of the life assured. This variant has a Return of Premiums (ROPs) benefit, which will be paid at the end of the Income Period, i.e. Policy term also, provided the life assured is alive then (ROP will be paid along with last Income Installment if the Income Installments are not preponed).However, if the Income Installments are preponed it will be paid at the end of the Income Period. 
+3. The Income Period will start after the end of deferment period, and Income Instalments are paid provided the life assured is alive at each instalment. 
+4. The Income Period always is up to age 120. (calculated as per last birthday) The Income Period: PT minus PPT minus deferment period (if any). 
+5. A constant (level) Income Instalment will be paid through-out the Income Period. 6. The maturity Benefit will be Return of Premiums plus Last Income Instalment (if not preponed)
+Variants | Death Benefit during PT | Income Benefit after deferment period | Lumpsum Benefit at Maturity | Surrender during PT
+Variant 1, 2, 3, 4 | Yes (by Default, in monthly income for 5 years) | No | No | Yes
+Variant 5 | Yes (by Default, in Lumpsum) | No (option: customer can take Lumpsum in installments for 5 / 10 years) | Yes | Yes
+Variant 6 | Yes (by default in instalments during the Death Benefit Instalment Period &amp; ROP at the end of Death Benefit Instalment Period) | Yes | Yes (at the end of the Income Period) | Yes</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>This is a non-linked, non-participating, single premium payment endowment plan.
+The plan provides death benefit, maturity benefit and surrender benefit.</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>life, individual, (Removed)
+single/regular → single
+payment, savings plan available on single and joint life basis and prashil wanjari business analyst b) → payment endowment plan.
+benefit during the Policy Term (PT) (under all variants), → benefit,
+(under all Variant), Income Benefit after Premium Payment Term (PPT) plus Deferment Period (DP) (under Variants 1, 2, 3 ,4 &amp; 6) (Removed)
+value (under all variants). All these benefits are detailed further in the sections below. The product has six (6) variants. i) Variant 1 – Lifelong Income: 1. The variant has a limited/regular premium payment option with Single life. The life cover is available during the policy term. On death of the life assured, the death benefit in instalments (as mentioned in the Benefits section below) will be paid, the policy will be terminated, and no further benefit is payable 2. At the end of the deferment period, provided the life assured is alive then, the Income Benefit is paid as instalments over the Income Period up to age 120 years of the life assured. This variant has a Return of Premiums (ROPs) benefit, which will be paid at the end of the Income Period, i.e. Policy term also, provided the life assured is alive then (ROP will be paid along with last Income Installment if the Income Installments are not preponed).However, if the Income Installments are preponed it will be paid at the end of the Income Period. 3. The Income Period will start after the end of deferment period, and Income Instalments are paid provided the life assured is alive at each instalment. 4. The Income Period always is up to age 120. (calculated as per last birthday) The Income Period: PT minus PPT minus deferment period (if any). 5. A constant (level) Income Instalment will be paid through-out the Income Period. 6. The maturity Benefit will be Return of Premiums plus Last Income Instalment (if not preponed) Variants | Death Benefit during PT | Income Benefit after deferment period | Lumpsum Benefit at Maturity | Surrender during PT Variant 1, 2, 3, 4 | Yes (by Default, in monthly income for 5 years) | No | No | Yes Variant 5 | Yes (by Default, in Lumpsum) | No (option: customer can take Lumpsum in installments for 5 / 10 years) | Yes | Yes Variant 6 | Yes (by default in instalments during the Death Benefit Instalment Period &amp; ROP at the end of Death Benefit Instalment Period) | Yes | Yes (at the end of the Income Period) | Yes → benefit.</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Value Changed</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Minimum/ Maximum Maturity Age</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Maturity Age (lbd) in years | Variant 1 - Lifelong Income | Variant 2 - Second Income | Variant 3 – Step-up Income | Variant 4 – Extra Income | Variant 5 – Wealth Creation | Variant 6 - Assured Income
+Minimum | 99 | 35 | 30 | 20 | 20 | 20
+Maximum Maturity Age | 99 | 92 | 89 | Single Life Policy: 75 Joint Life Policy ##: 60 | 74</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Premium Payment Frequency</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>The premium payment and benefit payment modes available are yearly, half yearly, quarterly and monthly. The quarterly and monthly mode of premium payment will be allowed only under auto-debit option (as approved by RBI from time-to-time).</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
+      <c r="U6" s="8" t="inlineStr"/>
+      <c r="V6" s="8" t="inlineStr"/>
+      <c r="W6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>For POS channel</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Maximum Maturity Age shall be 65 years
+ Only Single life will be available 
+ Maximum Policy Term is 40 years. 
+ Maximum Sum Assured is Rs. 50 lacs</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Options available under the product</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Option to take the yearly Income Instalments in other instalment frequencies (only in Variants 1 to 4 &amp; 6) and Death Benefit Instalments (only in Variants 6)
+The default option in the product is annual Income Instalment. But the policyholder will have an option to take the same in other-than-yearly instalments. The Income Installment frequency has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment frequency once again during the policy term but before the income period starts. He can choose half-yearly, quarterly or monthly 
+As per the Income Instalment frequency chosen by the policyholder, the instalments will be paid-out at the end of year, half-year, quarter or month from the end of the policy term, and at every subsequent half-year, quarter or month respectively. The half-yearly, quarterly or monthly installment will be arrived using the frequency factors given in above section “Income Instalments Frequency”, which will be applied on the yearly installment. 
+The policyholder will not have the flexibility to change this option during income period
+Death Benefit Instalment: As on the date of death, and at every subsequent half-year, quarter or month respectively. 
+Option to change the date of Income Instalment (only in Variants 1 to 4 &amp; 6) 
+The Income Installment date has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment date any time (no restrictions on number of changes) during the policy term but before the income period starts. Income Instalment date cannot be changed during the Income Period. 
+The default option in the product is Income Instalment become due in arrear, i.e., one year after the end of policy term. But the policyholder will have an option to prepone the start of Income Installments by a maximum of 365 days, still within the Income Period. In any case the Income Installments (opted in any frequency) cannot be postpone from the due date.
+For Ex: - In case of yearly Income Instalments A policy is issued on 1st Jan 2030 with a policy term of 10 years. The default first yearly Income Installment will be payable on 1st Jan 2032. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2040 (Maximum of 365 days within the Income Period). 
+In case of monthly Income Instalments A policy is issued on 1st Jan 2024 with a policy term of 10 years. The default first monthly Income Installment will be payable on 1st Feb 2045. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2040.</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr"/>
+      <c r="R8" s="8" t="inlineStr"/>
+      <c r="S8" s="8" t="inlineStr"/>
+      <c r="T8" s="8" t="inlineStr"/>
+      <c r="U8" s="8" t="inlineStr"/>
+      <c r="V8" s="8" t="inlineStr"/>
+      <c r="W8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
           <t>No Change</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>No Change</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>No Change</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Plan Description</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Plan Description</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>94.05</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>This is a non-linked, non-participating, single premium payment endowment plan.
+The plan provides death benefit, maturity benefit and surrender benefit.</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>This is a non-linked, life, individual, non-participating, single/limited/regular premium payment, savings plan available on single and joint life basis. 
 b) The plan provides death benefit during the Policy Term (PT) (under all variants), maturity benefit (under all Variant), Income Benefit after Premium Payment Term (PPT) plus Deferment Period (DP) (under Variants 1, 2, 3 ,4 &amp; 6) and surrender value (under all variants). All these benefits are detailed further in the sections below.
@@ -818,593 +1331,1158 @@
 Variant 6 | Yes (by default in instalments during the Death Benefit Instalment Period &amp; ROP at the end of Death Benefit Instalment Period) | Yes | Yes (at the end of the Income Period) | Yes</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>This is a non-linked, life, individual, non-participating, single/regular premium payment, savings plan available on single and joint life basis and prashil wanjari business analyst
-b) The plan provides death benefit during the Policy Term (PT) (under all variants), maturity benefit (under all Variant), Income Benefit after Premium Payment Term (PPT) plus Deferment Period (DP) (under Variants 1, 2, 3 ,4 &amp; 6) and surrender value (under all variants). All these benefits are detailed further in the sections below.
-The product has six (6) variants. i) Variant 1 – Lifelong Income: 1. The variant has a limited/regular premium payment option with Single life. The life cover is available during the policy term. On death of the life assured, the death benefit in instalments (as mentioned in the Benefits section below) will be paid, the policy will be terminated, and no further benefit is payable
-2. At the end of the deferment period, provided the life assured is alive then, the Income Benefit is paid as instalments over the Income Period up to age 120 years of the life assured. This variant has a Return of Premiums (ROPs) benefit, which will be paid at the end of the Income Period, i.e. Policy term also, provided the life assured is alive then (ROP will be paid along with last Income Installment if the Income Installments are not preponed).However, if the Income Installments are preponed it will be paid at the end of the Income Period. 
-3. The Income Period will start after the end of deferment period, and Income Instalments are paid provided the life assured is alive at each instalment. 
-4. The Income Period always is up to age 120. (calculated as per last birthday) The Income Period: PT minus PPT minus deferment period (if any). 
-5. A constant (level) Income Instalment will be paid through-out the Income Period. 6. The maturity Benefit will be Return of Premiums plus Last Income Instalment (if not preponed)
-Variants | Death Benefit during PT | Income Benefit after deferment period | Lumpsum Benefit at Maturity | Surrender during PT
-Variant 1, 2, 3, 4 | Yes (by Default, in monthly income for 5 years) | No | No | Yes
-Variant 5 | Yes (by Default, in Lumpsum) | No (option: customer can take Lumpsum in installments for 5 / 10 years) | Yes | Yes
-Variant 6 | Yes (by default in instalments during the Death Benefit Instalment Period &amp; ROP at the end of Death Benefit Instalment Period) | Yes | Yes (at the end of the Income Period) | Yes</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>single/limited/regular → single/regular
-basis. → basis and prashil wanjari business analyst
-99 → 120
-99. → 120.
-Yes → No</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>life, individual,
+single/limited/regular premium payment, savings plan available on
+premium payment endowment plan. → and joint life basis. b)
+benefit, → benefit during the Policy Term (PT) (under all variants),
+(under all Variant), Income Benefit after Premium Payment Term (PPT) plus Deferment Period (DP) (under Variants 1, 2, 3 ,4 &amp; 6)
+benefit. → value (under all variants). All these benefits are detailed further in the sections below. The product has six (6) variants. i) Variant 1 – Lifelong Income: 1. The variant has a limited/regular premium payment option with Single life. The life cover is available during the policy term. On death of the life assured, the death benefit in instalments (as mentioned in the Benefits section below) will be paid, the policy will be terminated, and no further benefit is payable 2. At the end of the deferment period, provided the life assured is alive then, the Income Benefit is paid as instalments over the Income Period up to age 99 years of the life assured. This variant has a Return of Premiums (ROPs) benefit, which will be paid at the end of the Income Period, i.e. Policy term also, provided the life assured is alive then (ROP will be paid along with last Income Installment if the Income Installments are not preponed).However, if the Income Installments are preponed it will be paid at the end of the Income Period. 3. The Income Period will start after the end of deferment period, and Income Instalments are paid provided the life assured is alive at each instalment. 4. The Income Period always is up to age 99. (calculated as per last birthday) The Income Period: PT minus PPT minus deferment period (if any). 5. A constant (level) Income Instalment will be paid through-out the Income Period. 6. The maturity Benefit will be Return of Premiums plus Last Income Instalment (if not preponed) Variants | Death Benefit during PT | Income Benefit after deferment period | Lumpsum Benefit at Maturity | Surrender during PT Variant 1, 2, 3, 4 | Yes (by Default, in monthly income for 5 years) | Yes | No | Yes Variant 5 | Yes (by Default, in Lumpsum) | No (option: customer can take Lumpsum in installments for 5 / 10 years) | Yes | Yes Variant 6 | Yes (by default in instalments during the Death Benefit Instalment Period &amp; ROP at the end of Death Benefit Instalment Period) | Yes | Yes (at the end of the Income Period) | Yes</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>Value Changed</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="P4" s="7" t="inlineStr">
-        <is>
-          <t>The plan description has been updated to reflect a change in the maximum age for income benefits from 99 to 120 years, and the wording has been modified to remove 'limited' from the premium payment options. Additionally, an extraneous phrase has been added to the description.</t>
-        </is>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>The plan description has been updated to reflect a change in the maximum age for income benefits from 99 to 120 years, and the wording has been modified to remove 'limited' from the premium payment options. Additionally, an extraneous phrase has been added to the description.</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>This change significantly extends the income benefit period for policyholders, potentially increasing the attractiveness of the product. It may also affect the product's competitive positioning in the market. The removal of 'limited' could imply a more flexible premium payment structure, which may attract a broader customer base.</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>Product, Actuarial, Operations, Customer Service, Compliance, Testing</t>
-        </is>
-      </c>
-      <c r="T4" s="7" t="inlineStr">
-        <is>
-          <t>UAT
-Regression Testing</t>
-        </is>
-      </c>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V4" s="7" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Unable to generate summary.</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr"/>
+      <c r="S10" s="8" t="inlineStr"/>
+      <c r="T10" s="8" t="inlineStr"/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Minimum Entry Age</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>For 1.5X Sum Assured:  
+0 years
+For Enhanced Sum Assured:
+0 years</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="W4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="55" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Minimum/ Maximum Maturity Age</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Minimum/ Maximum Maturity Age</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Maximum Entry Age</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>For Sum Assured : 60 years 
+For Enhanced Sum Assured:
+SP &lt;  1,00,000 | 44
+SP &gt;= 1,00,000 | 50</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr"/>
+      <c r="M12" s="8" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>99.87</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>99.94</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="R12" s="8" t="inlineStr"/>
+      <c r="S12" s="8" t="inlineStr"/>
+      <c r="T12" s="8" t="inlineStr"/>
+      <c r="U12" s="8" t="inlineStr"/>
+      <c r="V12" s="8" t="inlineStr"/>
+      <c r="W12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Minimum Maturity Age</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>18 years</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Maximum Age at Maturity</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>For 1.5X Sum Assured
+All channels except POS :	Age attained 80 years
+For POS Channel             :	Age attained 65 years
+For Enhanced Sum Assured
+Risk cover will commence immediately on issuance of the policy.
+The policy will vest on the life of the life assured at age 18 of the life assured.
+For POS Channel
+SP &lt;  1,00,000 | 64
+SP &gt;= 1,00,000 | 65
+All channels except POS:
+SP &lt;  1,00,000 | 64
+SP &gt;= 1,00,000 | 80</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr"/>
+      <c r="M14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="R14" s="8" t="inlineStr"/>
+      <c r="S14" s="8" t="inlineStr"/>
+      <c r="T14" s="8" t="inlineStr"/>
+      <c r="U14" s="8" t="inlineStr"/>
+      <c r="V14" s="8" t="inlineStr"/>
+      <c r="W14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Policy Term &amp; Premium paying Term</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>PT : 5, 7 &amp; 10 5 to 20 years
+PPT: This is a single premium product.</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr"/>
+      <c r="W15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Minimum and Maximum Sum Assured</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>SA options available: (i) 1.5 times the Single Premium or 
+(ii) 10 times the Single Premium. 
+If the 10 times SP is chosen, this will be referred to as Enhanced Sum Assured.
+If the policy is sold through POS Channel, the Maximum Sum Assured/Enhanced Sum Assured will be Rs.25 lacs, as per prevailing POS regulations /guidelines/circulars etc. 
+Note: The Single Premium mentioned above is the amount chosen by the policyholder and is excluding any extra premium loading.</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr"/>
+      <c r="M16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="R16" s="8" t="inlineStr"/>
+      <c r="S16" s="8" t="inlineStr"/>
+      <c r="T16" s="8" t="inlineStr"/>
+      <c r="U16" s="8" t="inlineStr"/>
+      <c r="V16" s="8" t="inlineStr"/>
+      <c r="W16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="55" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Minimum Premium</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Rs. 25,000</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="55" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Maximum Premium</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>As per board approved underwriting norms.</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr"/>
+      <c r="M18" s="8" t="inlineStr"/>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr"/>
+      <c r="R18" s="8" t="inlineStr"/>
+      <c r="S18" s="8" t="inlineStr"/>
+      <c r="T18" s="8" t="inlineStr"/>
+      <c r="U18" s="8" t="inlineStr"/>
+      <c r="V18" s="8" t="inlineStr"/>
+      <c r="W18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Death Benefit &amp; Maturity Benefit:</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>~ 	Sum Assured on Death is the higher of (i) Sum Assured,  (ii) Guaranteed Sum Assured on Maturity # (iii) Any absolute amount assured to be paid on death ^.
+In case Enhanced Sum Assured is chosen in the policy, 	
+~ Sum Assured on Death is the higher of (i) Enhanced Sum Assured##,  (ii) Guaranteed Sum Assured on Maturity # (iii) Any absolute amount assured to be paid on death ^.
+ * Total premium paid is the Single Premium paid in the policy, exclusive of extra premium and GST, if any. Please note that GST will be collected over and above the single premium under the policy.
+#	Guaranteed Sum Assured on Maturity is equal to the total premiums paid by the policyholder. 
+^	Any absolute amount assured to be paid on death is equal to the Sum Assured.
+Event | When Benefits are payable | Benefits/Policy Monies Payable
+Death Benefit: 
+Death of life assured during the policy term | If the policy is in-force | Sum Assured on Death~ as on date of death.
+The policy will terminate on payment of the death benefit.
+Guaranteed Maturity Benefit: 
+Survival of life assured to the maturity date | If the policy is in-force | GE% times the Total Premiums* paid 
+The guaranteed maturity benefit will be subject to minimum of 100% of the total premiums * paid.
+The policy will terminate on payment of the guaranteed maturity benefit.
+Note: The guaranteed maturity benefit for female lives shall be calculated with an age set-back of 3 years from the given Annexure I table which would only be applicable only Enhanced Sum Assured option.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="inlineStr"/>
+      <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Suicide Clause</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>If the life assured commit suicide, whether sane or insane, within twelve (12) months from the date of commencement of risk of the policy, the policy shall be terminated by paying the below mentioned amount.
+If the death is within twelve (12) months from the date of commencement of risk, the amount payable will be 80% of the single premium paid as on date of death.</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr"/>
+      <c r="M20" s="8" t="inlineStr"/>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr"/>
+      <c r="R20" s="8" t="inlineStr"/>
+      <c r="S20" s="8" t="inlineStr"/>
+      <c r="T20" s="8" t="inlineStr"/>
+      <c r="U20" s="8" t="inlineStr"/>
+      <c r="V20" s="8" t="inlineStr"/>
+      <c r="W20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Guaranteed Enhancer (GE)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>At the end of the policy term, on the maturity date, the guaranteed maturity benefit will be payable in a lump-sum, and it will be the total premiums* paid under the policy, enhanced by a percentage, called the Guaranteed Enhancer %. 
+The applicable GE% are as given in the attached Annexure I.
+This percentage will be applied on total premiums* paid.
+E.g., if the single premium (excluding any extra premium loading) chosen is 25,000, the PT is 7 years and the SA is 1.25 times, then, the guaranteed maturity benefit is 155% * 25,000 = 38,750.
+iv. This feature is not available for a surrendered policy.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="inlineStr"/>
+      <c r="V21" s="5" t="inlineStr"/>
+      <c r="W21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Additional Guaranteed Enhancer (Applicable for online, Direct Sales and Staff policies)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Additional Guaranteed Enhancer is applicable for policies sold through online channel, Direct Sales as per table below, and shall be applicable on the single premium paid. 
+Additional Guaranteed Enhancer is applicable for policies directly sold to staff, as per table below, and shall be applicable on the single premium paid. 
+The Additional Guaranteed Enhancer is applicable over and above the mentioned Guaranteed Enhancer.
+E.g., If the single premium (excluding any extra premium loading) chosen is 25,000, PT 7 yrs, SA 1.25 times and the policy purchased online, then, the guaranteed maturity benefit is (155%+1.75%) * 25,000 = 39,187.50.
+The guaranteed maturity benefit for female lives shall be calculated with an age set-back of 3 years from the given Annexure I table which would only be applicable on Enhanced Sum Assured option.
+Employees of Bajaj Allianz Life, Bajaj Allianz General, Allianz Group &amp; Bajaj Group and their spouse, children &amp; parents are referred to as “Staff” and they are all resident of India.</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr"/>
+      <c r="M22" s="8" t="inlineStr"/>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr"/>
+      <c r="R22" s="8" t="inlineStr"/>
+      <c r="S22" s="8" t="inlineStr"/>
+      <c r="T22" s="8" t="inlineStr"/>
+      <c r="U22" s="8" t="inlineStr"/>
+      <c r="V22" s="8" t="inlineStr"/>
+      <c r="W22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Riders Available</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>No Riders</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="inlineStr"/>
+      <c r="W23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="55" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Surrender Benefit</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>NO MATCH FOUND</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>No Match</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Added / Removed</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>The policyholder can surrender the policy at any time after the first policy year.
+The surrender benefit will be higher of guaranteed surrender value (GSV) or special surrender value (SSV).
+GSV factors are as per the table below. GSV factor will be applied on the Total Premiums* paid as on the date of surrender, to arrive at the GSV.
+The SSV is sum of SSV1 and SSV2.
+The amount of SSV1 will be arrived at by multiplying the sum assured on death with the SSV1 factor.
+The amount of SSV2 will be arrived at by multiplying the amount of Guaranteed Maturity Benefit with the SSV2 factor. 
+The SSV1 &amp; SSV2 factors are given in the attached Annexure II. These factors are not guaranteed and company will review these factors from time to time, subject to IRDAI approval.</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr"/>
+      <c r="M24" s="8" t="inlineStr"/>
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>New /Removed Parameter</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>No semantically similar parameter found.</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr"/>
+      <c r="R24" s="8" t="inlineStr"/>
+      <c r="S24" s="8" t="inlineStr"/>
+      <c r="T24" s="8" t="inlineStr"/>
+      <c r="U24" s="8" t="inlineStr"/>
+      <c r="V24" s="8" t="inlineStr"/>
+      <c r="W24" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Report Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Total Parameters</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>No Change</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Maturity Age (lbd) in years | Variant 1 - Lifelong Income | Variant 2 - Second Income | Variant 3 – Step-up Income | Variant 4 – Extra Income | Variant 5 – Wealth Creation | Variant 6 - Assured Income
-Minimum | 99 | 35 | 30 | 20 | 18 | 18
-Maximum | 99 | 92 | 89 | Single Life Policy: 75 Joint Life Policy ##: 60 | 74</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Maturity Age (lbd) in years | Variant 1 - Lifelong Income | Variant 2 - Second Income | Variant 3 – Step-up Income | Variant 4 – Extra Income | Variant 5 – Wealth Creation | Variant 6 - Assured Income
-Minimum | 99 | 35 | 30 | 20 | 20 | 20
-Maximum Maturity Age | 99 | 92 | 89 | Single Life Policy: 75 Joint Life Policy ##: 60 | 74</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>18 → 20
-18 → 20
-Maturity Age</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>Value Changed</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>The minimum maturity age for Variants 5 and 6 has been increased from 18 to 20 years.</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>The minimum maturity age for Variants 5 and 6 has been increased from 18 to 20 years.</t>
-        </is>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>This change affects the eligibility criteria for customers, potentially limiting access to certain products for younger policyholders. It may also influence the product's market positioning and competitiveness.</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>Product, Actuarial, Operations, Customer Service, Compliance, Data Migration, Testing</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>UAT
-Regression Testing</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="B29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Premium Payment Frequency</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Premium Payment Frequency</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>The premium payment and benefit payment modes available are yearly, half yearly, quarterly and monthly. The quarterly and monthly mode of premium payment will be allowed only under auto-debit option (as approved by RBI from time-to-time).</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>The premium payment and benefit payment modes available are yearly, half yearly, quarterly and monthly. The quarterly and monthly mode of premium payment will be allowed only under auto-debit option (as approved by RBI from time-to-time).</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>There is no change in the premium payment frequency parameters as both the old and new descriptions are identical.</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>There is no change in the premium payment frequency parameters as both the old and new descriptions are identical.</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>Since there is no change, there will be no impact on business operations, processes, or customer interactions.</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>Product, Operations, Customer Service, Compliance, IT, Testing</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>Regression Testing</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="n">
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Modified</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>For POS channel</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>For POS channel</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>97.22</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>98.61</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Maximum Maturity Age shall be 65 years
- Only Single life will be available 
- Maximum Policy Term is 20 years. 
- Maximum Sum Assured is Rs. 25 lacs</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Maximum Maturity Age shall be 65 years
- Only Single life will be available 
- Maximum Policy Term is 40 years. 
- Maximum Sum Assured is Rs. 50 lacs</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>20 → 40
-25 → 50</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>Value Changed</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>The maximum policy term has increased from 20 years to 40 years, and the maximum sum assured has increased from Rs. 25 lacs to Rs. 50 lacs for the POS channel.</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>The maximum policy term has increased from 20 years to 40 years, and the maximum sum assured has increased from Rs. 25 lacs to Rs. 50 lacs for the POS channel.</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>This change allows for longer policy terms and higher sum assured amounts, potentially attracting a broader customer base and increasing sales opportunities. It may also enhance the product's competitiveness in the market.</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>Product, Actuarial, Operations, Customer Service, Compliance, IT, Testing, Sales</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>UAT
-Regression Testing</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Options available under the product</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Options available under the product</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>99.79000000000001</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Option to take the yearly Income Instalments in other instalment frequencies (only in Variants 1 to 4 &amp; 6) and Death Benefit Instalments (only in Variants 6)
-The default option in the product is annual Income Instalment. But the policyholder will have an option to take the same in other-than-yearly instalments. The Income Installment frequency has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment frequency once again during the policy term but before the income period starts. He can choose half-yearly, quarterly or monthly 
-As per the Income Instalment frequency chosen by the policyholder, the instalments will be paid-out at the end of year, half-year, quarter or month from the end of the policy term, and at every subsequent half-year, quarter or month respectively. The half-yearly, quarterly or monthly installment will be arrived using the frequency factors given in above section “Income Instalments Frequency”, which will be applied on the yearly installment. 
-The policyholder will not have the flexibility to change this option during income period
-Death Benefit Instalment: As on the date of death, and at every subsequent half-year, quarter or month respectively. 
-Option to change the date of Income Instalment (only in Variants 1 to 4 &amp; 6) 
-The Income Installment date has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment date any time (no restrictions on number of changes) during the policy term but before the income period starts. Income Instalment date cannot be changed during the Income Period. 
-The default option in the product is Income Instalment become due in arrear, i.e., one year after the end of policy term. But the policyholder will have an option to prepone the start of Income Installments by a maximum of 365 days, still within the Income Period. In any case the Income Installments (opted in any frequency) cannot be postpone from the due date.
-For Ex: - In case of yearly Income Instalments A policy is issued on 1st Jan 2021 with a policy term of 10 years. The default first yearly Income Installment will be payable on 1st Jan 2032. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2031 (Maximum of 365 days within the Income Period). 
-In case of monthly Income Instalments A policy is issued on 1st Jan 2021 with a policy term of 10 years. The default first monthly Income Installment will be payable on 1st Feb 2031. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2031.</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>Option to take the yearly Income Instalments in other instalment frequencies (only in Variants 1 to 4 &amp; 6) and Death Benefit Instalments (only in Variants 6)
-The default option in the product is annual Income Instalment. But the policyholder will have an option to take the same in other-than-yearly instalments. The Income Installment frequency has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment frequency once again during the policy term but before the income period starts. He can choose half-yearly, quarterly or monthly 
-As per the Income Instalment frequency chosen by the policyholder, the instalments will be paid-out at the end of year, half-year, quarter or month from the end of the policy term, and at every subsequent half-year, quarter or month respectively. The half-yearly, quarterly or monthly installment will be arrived using the frequency factors given in above section “Income Instalments Frequency”, which will be applied on the yearly installment. 
-The policyholder will not have the flexibility to change this option during income period
-Death Benefit Instalment: As on the date of death, and at every subsequent half-year, quarter or month respectively. 
-Option to change the date of Income Instalment (only in Variants 1 to 4 &amp; 6) 
-The Income Installment date has to be chosen at inception. However, the policy holder will have an option to change the Income Instalment date any time (no restrictions on number of changes) during the policy term but before the income period starts. Income Instalment date cannot be changed during the Income Period. 
-The default option in the product is Income Instalment become due in arrear, i.e., one year after the end of policy term. But the policyholder will have an option to prepone the start of Income Installments by a maximum of 365 days, still within the Income Period. In any case the Income Installments (opted in any frequency) cannot be postpone from the due date.
-For Ex: - In case of yearly Income Instalments A policy is issued on 1st Jan 2030 with a policy term of 10 years. The default first yearly Income Installment will be payable on 1st Jan 2032. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2040 (Maximum of 365 days within the Income Period). 
-In case of monthly Income Instalments A policy is issued on 1st Jan 2024 with a policy term of 10 years. The default first monthly Income Installment will be payable on 1st Feb 2045. The policy holder will have an option to prepone the Income Installment date upto 1st Jan 2040.</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>2021 → 2030
-2031 → 2040
-2021 → 2024
-2031. → 2045.
-2031. → 2040.</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>Value Changed</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>The change involves updates to the Income Instalment options and the dates for when these instalments can be prepone, specifically changing the years from 2021 to 2030 and 2031 to 2040, affecting the timing of payments for new policies.</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>The change involves updates to the Income Instalment options and the dates for when these instalments can be prepone, specifically changing the years from 2021 to 2030 and 2031 to 2040, affecting the timing of payments for new policies.</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>This change allows policyholders greater flexibility in choosing their Income Instalment dates and frequencies, potentially enhancing customer satisfaction and retention. It may also impact cash flow projections for the company due to changes in payment timings.</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>Product, Actuarial, Operations, Customer Service, Compliance, IT, Testing</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>UAT
-Regression Testing</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Report Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Total Parameters</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>No Change</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Modified</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Added / Removed</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="B31" s="13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Generated by Product Change Analyzer | Enterprise AI Business Impact Engine</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W8"/>
+  <autoFilter ref="A1:W24"/>
   <mergeCells count="2">
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A18:W18"/>
+    <mergeCell ref="A34:W34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
